--- a/docs/design/ACSMS-SCR-019/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_販売店Excelデータ取込画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-019/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_販売店Excelデータ取込画面_v1.0.xlsx
@@ -7447,7 +7447,7 @@
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="46" t="inlineStr">
         <is>
-          <t>NICHINO_STAFF による販売店Excelデータ取込 — 代行入力可</t>
+          <t>NICHINO_STAFF による販売店Excelデータ取込 — 権限なし（403）</t>
         </is>
       </c>
       <c r="F14" s="10" t="n"/>
@@ -7458,7 +7458,7 @@
         <is>
           <t>・role: NICHINO_STAFF
 ・ログイン済 + MFA認証済
-・権限 `hanbaiten.import` 保有
+・権限 `hanbaiten.import` **非保有**（2026-06 剥奪 — migration 1711900900017）
 ・対象JA：ja-002 配下に取込対象のテンプレートExcelファイルを用意</t>
         </is>
       </c>
@@ -7484,7 +7484,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">サイドバーで「販売店Excelデータ取込」項目を確認し、URL `/hanbaiten/import` にアクセス
+            <t xml:space="preserve">サイドバー／ダッシュボードに「販売店Excelデータ取込」メニューが表示されないことを確認
 </t>
           </r>
           <r>
@@ -7501,7 +7501,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ja-002 のテンプレートExcelをアップロード、取込モード「新規登録」を選択
+            <t xml:space="preserve">URL `/hanbaiten/import` に直接アクセス、または `POST /api/v1/hanbaiten/import` を直接呼び出す
 </t>
           </r>
           <r>
@@ -7518,24 +7518,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">取込開始ボタン押下 → 確認ダイアログ「はい」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DB 確認: `SELECT * FROM m_hanbaiten WHERE ja_id = 2 ORDER BY created_at DESC LIMIT 5`</t>
+            <t>取込リクエストを送信する</t>
           </r>
         </is>
       </c>
@@ -7561,7 +7544,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">販売店Excelデータ取込画面が表示されること（DataScope 全JAアクセス可、代行入力権限保有）
+            <t xml:space="preserve">権限ガード（`hanbaiten.import` 非保有）により、サイドバー／ダッシュボードに「販売店Excelデータ取込」メニューが表示されないこと
 </t>
           </r>
           <r>
@@ -7578,7 +7561,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビューエリアにアップロードファイルの内容が表示されること、列パネルが展開状態で全列チェック済みであること
+            <t xml:space="preserve">画面アクセス時はルーターガードでブロックされ、ダッシュボードへ遷移すること（`message.error('この画面へのアクセス権限がありません。')`）
 </t>
           </r>
           <r>
@@ -7595,24 +7578,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること（`message: "正常に取り込みました。"`）、取込件数がトーストで表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ja-002 配下に対象データが新規登録されていること、`created_by` が NICHINO_STAFF のテストアカウントと一致すること
+            <t xml:space="preserve">HTTPステータスコード403が返却されること（`error_code: FORBIDDEN`、`message: "この画面へのアクセス権限がありません。"`）、DB に登録されないこと
 </t>
           </r>
           <r>
@@ -7629,15 +7595,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・NICHINO_STAFF は `hanbaiten.daiko_input` 権限保有のため、他JAの販売店データを代行入力可能
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`account_concept.md` の販売店管理※2 規定に従う</t>
+            <t xml:space="preserve">・販売店Excelデータ取込（一括取込 `hanbaiten.import`）は CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN のみ保有。NICHINO_STAFF / NICHINO_ADMIN は非保有。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・NICHINO_STAFF の代行入力（`hanbaiten.daiko_input`）は販売店の個別 新規登録・修正に限り可能で、Excel一括取込は対象外。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`seeder.md §3` + `account_concept.md` の販売店Excelデータ取込行（NICHINO_STAFF=×）に従う</t>
           </r>
         </is>
       </c>
@@ -7649,7 +7623,7 @@
       <c r="AD14" s="11" t="n"/>
       <c r="AE14" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF14" s="11" t="n"/>
@@ -7685,7 +7659,7 @@
       <c r="BJ14" s="11" t="n"/>
       <c r="BK14" s="46" t="inlineStr">
         <is>
-          <t>NICHINO_STAFFは販売店代行入力により各JAの販売店の新規登録・修正が可能。</t>
+          <t>NICHINO_STAFF は Excel一括取込権限 `hanbaiten.import` を持たない（2026-06 剥奪）。販売店の個別代行入力（新規登録・修正、`hanbaiten.daiko_input`）は引き続き可能だが、Excel一括取込は不可。失敗時（STAFF が 200 で取込成功）は RBAC バイパスを意味する。</t>
         </is>
       </c>
       <c r="BL14" s="10" t="n"/>
@@ -12253,7 +12227,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、`total_rows: 500` で取込結果が返却されること、`message: "正常に取り込みました。"`
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、`total_rows: 500` で取込結果が返却されること、`message: "取り込みました。"`
 </t>
           </r>
           <r>
@@ -13369,7 +13343,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、レスポンスは `import_mode: "NEW"`, `total_rows: 3`, `created_count: 3`, `updated_count: 0`, `skipped_count: 0`, `message: "正常に取り込みました。"`
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、レスポンスは `import_mode: "NEW"`, `total_rows: 3`, `created_count: 3`, `updated_count: 0`, `skipped_count: 0`, `message: "取り込みました。"`
 </t>
           </r>
           <r>
@@ -14603,7 +14577,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB 確認: `SELECT * FROM t_log WHERE operation = 'IMPORT_UPDATE_ALL' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t>DB 確認: `SELECT * FROM t_log WHERE operation = 'IMPORT_UPDATE' ORDER BY log_datetime DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -14646,7 +14620,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、`updated_count: 1`, `created_count: 0`, `message: "正常に取り込みました。"`
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、`updated_count: 1`, `created_count: 0`, `message: "取り込みました。"`
 </t>
           </r>
           <r>
